--- a/src/backend/analyze/Data Model - Vectorstore Eval.xlsx
+++ b/src/backend/analyze/Data Model - Vectorstore Eval.xlsx
@@ -1,16 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11207"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wenye/SideProjects/Data Model/Stream-Assistant/Stream-Assistant/src/backend/analyze/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D9DBCA-E44C-6A4D-8C1C-A8E5EAA1F3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-38400" yWindow="-2860" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="1230"/>
-    <sheet r:id="rId2" sheetId="2" name="工作表2"/>
+    <sheet name="1230" sheetId="1" r:id="rId1"/>
+    <sheet name="工作表2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -137,132 +143,131 @@
     <t>Answer</t>
   </si>
   <si>
-    <t>建構可擴展分散式系統的最佳工具有哪些？</t>
-  </si>
-  <si>
     <t>distributed, Distributed Locks, http, reverse-proxy</t>
   </si>
   <si>
-    <t>心理學如何影響科技在社會中的採用？</t>
-  </si>
-  <si>
     <t>psychology, technology, society, lifestyle</t>
   </si>
   <si>
-    <t>為行動開發學習 Kotlin Multiplatform 有哪些好處？</t>
-  </si>
-  <si>
     <t>kotlin-multiplatform, android, ios, education</t>
   </si>
   <si>
-    <t>平面設計如何提升社群媒體上的用戶參與度？</t>
-  </si>
-  <si>
     <t>graphic-design, social-media, images, lifestyle</t>
   </si>
   <si>
-    <t>軟體開發接案需要掌握哪些技能？</t>
-  </si>
-  <si>
     <t>freelancing, front end, freelance-writing, javascript</t>
   </si>
   <si>
-    <t>深度學習如何促進大數據分析？</t>
-  </si>
-  <si>
     <t>deep-learning, Big Data, ai, python</t>
   </si>
   <si>
-    <t>實作正向與反向代理時有哪些安全考量？</t>
-  </si>
-  <si>
     <t>reverse-proxy, forwarding-proxy, firewall, network</t>
   </si>
   <si>
-    <t>remarkable-tablets 在筆記與生產力方面有何特色？</t>
-  </si>
-  <si>
     <t>remarkable-tablet, notes, work, lifestyle</t>
   </si>
   <si>
-    <t>遠距工作如何提升生產力與健康？</t>
-  </si>
-  <si>
     <t>work-from-home, work, health, self-improvement</t>
   </si>
   <si>
-    <t>使用 Golang 建立基於 websocket 的應用程式有何優勢？</t>
-  </si>
-  <si>
     <t>golang, websocket, http, network</t>
   </si>
   <si>
-    <t>如何利用 React 和 React Native 開發跨平台應用？</t>
-  </si>
-  <si>
     <t>react, react-native, javascript, android</t>
   </si>
   <si>
-    <t>AI 生成內容 (AIGC) 將如何改變設計工作流程？</t>
-  </si>
-  <si>
     <t>AIGC, graphic-design, ai, image-generation</t>
   </si>
   <si>
-    <t>如何改善 HTTP 網路請求的性能？</t>
-  </si>
-  <si>
     <t>http, network, forwarding-proxy, reverse-proxy</t>
   </si>
   <si>
-    <t>分散式鎖 (Distributed Locks) 如何提升系統的一致性？</t>
-  </si>
-  <si>
     <t>Distributed Locks, distributed, network, golang</t>
   </si>
   <si>
-    <t>使用 Splunk 進行日誌分析的最佳實踐有哪些？</t>
-  </si>
-  <si>
     <t>splunk, detection-engineering, Big Data, network</t>
   </si>
   <si>
-    <t>如何設計前端界面來提高用戶的可用性？</t>
+    <t>work, lifestyle, health, self-improvement</t>
+  </si>
+  <si>
+    <t>ios, technology, future, macos</t>
+  </si>
+  <si>
+    <t>image-generation, ai, deep-learning, Big Data</t>
+  </si>
+  <si>
+    <t>Big Data, ai, python, distributed</t>
   </si>
   <si>
     <t>front end, javascript, css</t>
   </si>
   <si>
-    <t>工作與生活平衡該如何達成？</t>
-  </si>
-  <si>
-    <t>work, lifestyle, health, self-improvement</t>
-  </si>
-  <si>
-    <t>iOS 系統的未來技術趨勢有哪些？</t>
-  </si>
-  <si>
-    <t>ios, technology, future, macos</t>
-  </si>
-  <si>
-    <t>如何提升 AI 在圖片生成中的真實性？</t>
-  </si>
-  <si>
-    <t>image-generation, ai, deep-learning, Big Data</t>
-  </si>
-  <si>
-    <t>如何使用 BigQuery 進行大數據分析？</t>
-  </si>
-  <si>
-    <t>Big Data, ai, python, distributed</t>
+    <t>我想建構一個擴展性高的分散式系統，有哪些工具可以用？</t>
+  </si>
+  <si>
+    <t>心理學在科技產品被人接受的過程中，會有哪些影響？</t>
+  </si>
+  <si>
+    <t>學 Kotlin Multiplatform 對於行動開發有什麼幫助？</t>
+  </si>
+  <si>
+    <t>怎麼用平面設計來提高社群媒體上的互動率？</t>
+  </si>
+  <si>
+    <t>接案做軟體開發需要學會哪些技能才夠用？</t>
+  </si>
+  <si>
+    <t>深度學習技術要怎麼應用在大數據分析上？</t>
+  </si>
+  <si>
+    <t>正向代理和反向代理的安全性要注意什麼問題？</t>
+  </si>
+  <si>
+    <t>remarkable-tablets 對於筆記和提升效率好用嗎？</t>
+  </si>
+  <si>
+    <t>遠距工作的時候，有哪些方法可以讓自己更有效率又健康？</t>
+  </si>
+  <si>
+    <t>用 Golang 寫 websocket 應用程式的好處是什麼？</t>
+  </si>
+  <si>
+    <t>如何用 React 或 React Native 快速做跨平台開發？</t>
+  </si>
+  <si>
+    <t>AI 生成內容 (AIGC) 怎麼影響設計師的工作流程？</t>
+  </si>
+  <si>
+    <t>怎樣優化 HTTP 網路請求的效能？</t>
+  </si>
+  <si>
+    <t>分散式鎖 (Distributed Locks) 怎麼提升系統穩定性？</t>
+  </si>
+  <si>
+    <t>使用 Splunk 做日誌分析，有哪些實用的技巧？</t>
+  </si>
+  <si>
+    <t>前端設計怎麼做才能讓用戶覺得更好用？</t>
+  </si>
+  <si>
+    <t>遠距工作和生活怎麼平衡？</t>
+  </si>
+  <si>
+    <t>iOS 系統有哪些未來的技術趨勢值得關注？</t>
+  </si>
+  <si>
+    <t>怎麼讓 AI 生成的圖片看起來更真實？</t>
+  </si>
+  <si>
+    <t>用 BigQuery 做大數據分析，適合哪些場景？</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,6 +287,14 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -312,25 +325,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -341,10 +355,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
@@ -382,71 +396,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -474,7 +488,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -497,11 +511,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -510,13 +524,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -526,7 +540,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -535,7 +549,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -544,7 +558,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -552,10 +566,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -620,184 +634,189 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" style="2" width="41.14785714285715" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="2" width="45.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="41.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21.75">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21.75">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="5" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21.75">
-      <c r="A4" s="1" t="s">
+    <row r="6" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="7" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21.75">
-      <c r="A5" s="1" t="s">
+    <row r="8" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="1" t="s">
+    </row>
+    <row r="9" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="21.75">
-      <c r="A6" s="1" t="s">
+    <row r="10" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="1" t="s">
+    </row>
+    <row r="11" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="21.75">
-      <c r="A7" s="1" t="s">
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="1" t="s">
+    </row>
+    <row r="13" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="21.75">
-      <c r="A8" s="1" t="s">
+    <row r="14" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="1" t="s">
+    </row>
+    <row r="15" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="21.75">
-      <c r="A9" s="1" t="s">
+    <row r="16" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="1" t="s">
+    </row>
+    <row r="17" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="21.75">
-      <c r="A10" s="1" t="s">
+    <row r="19" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="1" t="s">
+    </row>
+    <row r="20" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="21.75">
-      <c r="A11" s="1" t="s">
+    <row r="21" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="21.75">
-      <c r="A12" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="21.75">
-      <c r="A13" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="21.75">
-      <c r="A14" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="21.75">
-      <c r="A15" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="21.75">
-      <c r="A16" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="21.75">
-      <c r="A17" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="21.75">
-      <c r="A18" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="21.75">
-      <c r="A19" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="21.75">
-      <c r="A20" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="21.75">
-      <c r="A21" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>79</v>
-      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -805,18 +824,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" style="2" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="2" width="12.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="2" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
+    <row r="1" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -824,7 +842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25">
+    <row r="2" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -832,7 +850,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
+    <row r="3" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -840,7 +858,7 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
+    <row r="4" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -848,7 +866,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
+    <row r="5" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -856,7 +874,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
+    <row r="6" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -864,7 +882,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
+    <row r="7" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -872,7 +890,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
+    <row r="8" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -880,7 +898,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="17.25">
+    <row r="9" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -888,7 +906,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="17.25">
+    <row r="10" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -896,7 +914,7 @@
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25">
+    <row r="11" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -904,7 +922,7 @@
         <v>21</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25">
+    <row r="12" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -912,7 +930,7 @@
         <v>23</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="17.25">
+    <row r="13" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -920,7 +938,7 @@
         <v>25</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="17.25">
+    <row r="14" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -928,7 +946,7 @@
         <v>27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="17.25">
+    <row r="15" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
@@ -936,7 +954,7 @@
         <v>29</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25">
+    <row r="16" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -944,7 +962,7 @@
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="17.25">
+    <row r="17" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
@@ -952,7 +970,7 @@
         <v>33</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="17.25">
+    <row r="18" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -960,7 +978,7 @@
         <v>35</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="17.25">
+    <row r="19" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
